--- a/source_data/10_validation_guides/CDK2_4_6_validation_guides.xlsx
+++ b/source_data/10_validation_guides/CDK2_4_6_validation_guides.xlsx
@@ -1,27 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/samgould/Documents/GitHub/CDK-BE-mutagenesis/source_data/10_validation_guides/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E9E5A9F-6C54-7645-B921-B23D733A6CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BE91149-676D-5545-8B2A-143EDAF7BFD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="120">
   <si>
     <t>Name</t>
   </si>
@@ -327,13 +340,67 @@
   </si>
   <si>
     <t>#</t>
+  </si>
+  <si>
+    <t>Spacer</t>
+  </si>
+  <si>
+    <t>Sequenced</t>
+  </si>
+  <si>
+    <t>Match?</t>
+  </si>
+  <si>
+    <t>GCTGCTTATTAACACAGAGG</t>
+  </si>
+  <si>
+    <t>GTTAAGCTCCTTAAGCAGAG</t>
+  </si>
+  <si>
+    <t>GAAATTCAAAAACCAGGTAG</t>
+  </si>
+  <si>
+    <t>GAGAAATTCAAAAACCAGGT</t>
+  </si>
+  <si>
+    <t>GCCTCACGAACTGTGCTGAT</t>
+  </si>
+  <si>
+    <t>GTTGTCACCAGAATGTTCTC</t>
+  </si>
+  <si>
+    <t>GTGCCAATTGCATCGTTCAC</t>
+  </si>
+  <si>
+    <t>GGCATGTAGACCAGGACCTA</t>
+  </si>
+  <si>
+    <t>GCCTTCCCATCAGCACAGTT</t>
+  </si>
+  <si>
+    <t>GGGTCAAGTCTTGATCGACA</t>
+  </si>
+  <si>
+    <t>Sample #</t>
+  </si>
+  <si>
+    <t>GAGCGGCATGCCCTCCTCGC</t>
+  </si>
+  <si>
+    <t>GGCCTCCGTTCTTCAAGTCG</t>
+  </si>
+  <si>
+    <t>GGGGAGGGCGCCTATGGGAA</t>
+  </si>
+  <si>
+    <t>GCTCTGGCTAGTCCAAAGTC</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -365,6 +432,14 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -402,7 +477,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -410,6 +485,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -712,16 +800,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="29.5" customWidth="1"/>
     <col min="4" max="4" width="11.6640625" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="5" max="6" width="16.33203125" customWidth="1"/>
+    <col min="7" max="7" width="32.33203125" customWidth="1"/>
+    <col min="8" max="8" width="33" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -737,8 +827,20 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F1" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -751,8 +853,22 @@
       <c r="E2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="str">
+        <f>RIGHT(B2, 20)</f>
+        <v>GCTGCTTATTAACACAGAGG</v>
+      </c>
+      <c r="H2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I2" t="b">
+        <f>G2=H2</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -765,8 +881,22 @@
       <c r="E3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3" t="str">
+        <f>RIGHT(B3, 20)</f>
+        <v>GTTAAGCTCCTTAAGCAGAG</v>
+      </c>
+      <c r="H3" t="s">
+        <v>106</v>
+      </c>
+      <c r="I3" t="b">
+        <f>G3=H3</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -779,8 +909,22 @@
       <c r="E4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4" t="str">
+        <f>RIGHT(B4, 20)</f>
+        <v>GAAATTCAAAAACCAGGTAG</v>
+      </c>
+      <c r="H4" t="s">
+        <v>107</v>
+      </c>
+      <c r="I4" t="b">
+        <f t="shared" ref="I4:I15" si="0">G4=H4</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -793,8 +937,22 @@
       <c r="E5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5" t="str">
+        <f>RIGHT(B5, 20)</f>
+        <v>GAGAAATTCAAAAACCAGGT</v>
+      </c>
+      <c r="H5" t="s">
+        <v>108</v>
+      </c>
+      <c r="I5" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -807,8 +965,22 @@
       <c r="E6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6" t="str">
+        <f>RIGHT(B6, 20)</f>
+        <v>GCTCTGGCTAGTCCAAAGTC</v>
+      </c>
+      <c r="H6" t="s">
+        <v>119</v>
+      </c>
+      <c r="I6" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -821,8 +993,22 @@
       <c r="E7" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F7">
+        <v>7</v>
+      </c>
+      <c r="G7" t="str">
+        <f>RIGHT(B7, 20)</f>
+        <v>GTTGTCACCAGAATGTTCTC</v>
+      </c>
+      <c r="H7" t="s">
+        <v>110</v>
+      </c>
+      <c r="I7" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -835,8 +1021,22 @@
       <c r="E8" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F8">
+        <v>6</v>
+      </c>
+      <c r="G8" t="str">
+        <f>RIGHT(B8, 20)</f>
+        <v>GCCTCACGAACTGTGCTGAT</v>
+      </c>
+      <c r="H8" t="s">
+        <v>109</v>
+      </c>
+      <c r="I8" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -849,8 +1049,22 @@
       <c r="E9" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F9">
+        <v>8</v>
+      </c>
+      <c r="G9" t="str">
+        <f>RIGHT(B9, 20)</f>
+        <v>GTGCCAATTGCATCGTTCAC</v>
+      </c>
+      <c r="H9" t="s">
+        <v>111</v>
+      </c>
+      <c r="I9" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -863,8 +1077,22 @@
       <c r="E10" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F10">
+        <v>9</v>
+      </c>
+      <c r="G10" t="str">
+        <f>RIGHT(B10, 20)</f>
+        <v>GGCATGTAGACCAGGACCTA</v>
+      </c>
+      <c r="H10" t="s">
+        <v>112</v>
+      </c>
+      <c r="I10" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -877,8 +1105,22 @@
       <c r="E11" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F11">
+        <v>10</v>
+      </c>
+      <c r="G11" t="str">
+        <f>RIGHT(B11, 20)</f>
+        <v>GCCTTCCCATCAGCACAGTT</v>
+      </c>
+      <c r="H11" t="s">
+        <v>113</v>
+      </c>
+      <c r="I11" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -891,8 +1133,22 @@
       <c r="E12" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F12">
+        <v>11</v>
+      </c>
+      <c r="G12" t="str">
+        <f>RIGHT(B12, 20)</f>
+        <v>GGGTCAAGTCTTGATCGACA</v>
+      </c>
+      <c r="H12" t="s">
+        <v>114</v>
+      </c>
+      <c r="I12" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -905,8 +1161,22 @@
       <c r="E13" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F13">
+        <v>12</v>
+      </c>
+      <c r="G13" t="str">
+        <f>RIGHT(B13, 20)</f>
+        <v>GAGCGGCATGCCCTCCTCGC</v>
+      </c>
+      <c r="H13" t="s">
+        <v>116</v>
+      </c>
+      <c r="I13" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -919,8 +1189,22 @@
       <c r="E14" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F14">
+        <v>13</v>
+      </c>
+      <c r="G14" t="str">
+        <f>RIGHT(B14, 20)</f>
+        <v>GGCCTCCGTTCTTCAAGTCG</v>
+      </c>
+      <c r="H14" t="s">
+        <v>117</v>
+      </c>
+      <c r="I14" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -933,8 +1217,22 @@
       <c r="E15" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F15">
+        <v>14</v>
+      </c>
+      <c r="G15" t="str">
+        <f>RIGHT(B15, 20)</f>
+        <v>GGGGAGGGCGCCTATGGGAA</v>
+      </c>
+      <c r="H15" t="s">
+        <v>118</v>
+      </c>
+      <c r="I15" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -1132,6 +1430,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -1142,12 +1441,12 @@
   <cols>
     <col min="1" max="1" width="7.6640625" customWidth="1"/>
     <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="4" max="4" width="14.6640625" customWidth="1"/>
+    <col min="4" max="4" width="8.1640625" style="7" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="13.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>101</v>
       </c>
@@ -1157,7 +1456,7 @@
       <c r="C1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E1" s="3" t="s">
@@ -1167,7 +1466,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1177,7 +1476,7 @@
       <c r="C2" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="6" t="s">
         <v>70</v>
       </c>
       <c r="E2" s="4">
@@ -1188,7 +1487,7 @@
       </c>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1198,7 +1497,7 @@
       <c r="C3" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="6" t="s">
         <v>73</v>
       </c>
       <c r="E3" s="4">
@@ -1209,7 +1508,7 @@
       </c>
       <c r="G3" s="2"/>
     </row>
-    <row r="4" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1219,7 +1518,7 @@
       <c r="C4" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="6" t="s">
         <v>75</v>
       </c>
       <c r="E4" s="4">
@@ -1230,7 +1529,7 @@
       </c>
       <c r="G4" s="2"/>
     </row>
-    <row r="5" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1240,7 +1539,7 @@
       <c r="C5" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="6" t="s">
         <v>77</v>
       </c>
       <c r="E5" s="4">
@@ -1251,7 +1550,7 @@
       </c>
       <c r="G5" s="2"/>
     </row>
-    <row r="6" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1261,7 +1560,7 @@
       <c r="C6" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="6" t="s">
         <v>79</v>
       </c>
       <c r="E6" s="4">
@@ -1272,7 +1571,7 @@
       </c>
       <c r="G6" s="2"/>
     </row>
-    <row r="7" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1282,7 +1581,7 @@
       <c r="C7" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="6" t="s">
         <v>82</v>
       </c>
       <c r="E7" s="4">
@@ -1293,7 +1592,7 @@
       </c>
       <c r="G7" s="2"/>
     </row>
-    <row r="8" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1303,7 +1602,7 @@
       <c r="C8" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="6" t="s">
         <v>87</v>
       </c>
       <c r="E8" s="4">
@@ -1314,7 +1613,7 @@
       </c>
       <c r="G8" s="2"/>
     </row>
-    <row r="9" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1324,7 +1623,7 @@
       <c r="C9" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="6" t="s">
         <v>90</v>
       </c>
       <c r="E9" s="4">
@@ -1335,7 +1634,7 @@
       </c>
       <c r="G9" s="2"/>
     </row>
-    <row r="10" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1345,7 +1644,7 @@
       <c r="C10" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="6" t="s">
         <v>92</v>
       </c>
       <c r="E10" s="4">
@@ -1356,7 +1655,7 @@
       </c>
       <c r="G10" s="2"/>
     </row>
-    <row r="11" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1366,7 +1665,7 @@
       <c r="C11" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="6" t="s">
         <v>94</v>
       </c>
       <c r="E11" s="4">
@@ -1377,7 +1676,7 @@
       </c>
       <c r="G11" s="2"/>
     </row>
-    <row r="12" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1387,7 +1686,7 @@
       <c r="C12" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="6" t="s">
         <v>85</v>
       </c>
       <c r="E12" s="4">
@@ -1398,7 +1697,7 @@
       </c>
       <c r="G12" s="2"/>
     </row>
-    <row r="13" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1408,7 +1707,7 @@
       <c r="C13" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="6" t="s">
         <v>96</v>
       </c>
       <c r="E13" s="4">
@@ -1419,7 +1718,7 @@
       </c>
       <c r="G13" s="2"/>
     </row>
-    <row r="14" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1429,7 +1728,7 @@
       <c r="C14" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="6" t="s">
         <v>98</v>
       </c>
       <c r="E14" s="4">
@@ -1440,7 +1739,7 @@
       </c>
       <c r="G14" s="2"/>
     </row>
-    <row r="15" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1450,7 +1749,7 @@
       <c r="C15" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E15" s="4">
@@ -1466,5 +1765,6 @@
     <sortCondition ref="C2:C15"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/source_data/10_validation_guides/CDK2_4_6_validation_guides.xlsx
+++ b/source_data/10_validation_guides/CDK2_4_6_validation_guides.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/samgould/Documents/GitHub/CDK-BE-mutagenesis/source_data/10_validation_guides/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BE91149-676D-5545-8B2A-143EDAF7BFD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFD19A7F-FF0C-CC43-8AA2-3B062D903B27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -477,26 +477,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -827,16 +828,16 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="4" t="s">
         <v>104</v>
       </c>
     </row>
@@ -857,7 +858,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="str">
-        <f>RIGHT(B2, 20)</f>
+        <f t="shared" ref="G2:G15" si="0">RIGHT(B2, 20)</f>
         <v>GCTGCTTATTAACACAGAGG</v>
       </c>
       <c r="H2" t="s">
@@ -885,7 +886,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="str">
-        <f>RIGHT(B3, 20)</f>
+        <f t="shared" si="0"/>
         <v>GTTAAGCTCCTTAAGCAGAG</v>
       </c>
       <c r="H3" t="s">
@@ -913,14 +914,14 @@
         <v>3</v>
       </c>
       <c r="G4" t="str">
-        <f>RIGHT(B4, 20)</f>
+        <f t="shared" si="0"/>
         <v>GAAATTCAAAAACCAGGTAG</v>
       </c>
       <c r="H4" t="s">
         <v>107</v>
       </c>
       <c r="I4" t="b">
-        <f t="shared" ref="I4:I15" si="0">G4=H4</f>
+        <f t="shared" ref="I4:I15" si="1">G4=H4</f>
         <v>1</v>
       </c>
     </row>
@@ -941,14 +942,14 @@
         <v>4</v>
       </c>
       <c r="G5" t="str">
-        <f>RIGHT(B5, 20)</f>
+        <f t="shared" si="0"/>
         <v>GAGAAATTCAAAAACCAGGT</v>
       </c>
       <c r="H5" t="s">
         <v>108</v>
       </c>
       <c r="I5" t="b">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -969,14 +970,14 @@
         <v>5</v>
       </c>
       <c r="G6" t="str">
-        <f>RIGHT(B6, 20)</f>
+        <f t="shared" si="0"/>
         <v>GCTCTGGCTAGTCCAAAGTC</v>
       </c>
       <c r="H6" t="s">
         <v>119</v>
       </c>
       <c r="I6" t="b">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -997,14 +998,14 @@
         <v>7</v>
       </c>
       <c r="G7" t="str">
-        <f>RIGHT(B7, 20)</f>
+        <f t="shared" si="0"/>
         <v>GTTGTCACCAGAATGTTCTC</v>
       </c>
       <c r="H7" t="s">
         <v>110</v>
       </c>
       <c r="I7" t="b">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -1025,14 +1026,14 @@
         <v>6</v>
       </c>
       <c r="G8" t="str">
-        <f>RIGHT(B8, 20)</f>
+        <f t="shared" si="0"/>
         <v>GCCTCACGAACTGTGCTGAT</v>
       </c>
       <c r="H8" t="s">
         <v>109</v>
       </c>
       <c r="I8" t="b">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -1053,14 +1054,14 @@
         <v>8</v>
       </c>
       <c r="G9" t="str">
-        <f>RIGHT(B9, 20)</f>
+        <f t="shared" si="0"/>
         <v>GTGCCAATTGCATCGTTCAC</v>
       </c>
       <c r="H9" t="s">
         <v>111</v>
       </c>
       <c r="I9" t="b">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -1081,14 +1082,14 @@
         <v>9</v>
       </c>
       <c r="G10" t="str">
-        <f>RIGHT(B10, 20)</f>
+        <f t="shared" si="0"/>
         <v>GGCATGTAGACCAGGACCTA</v>
       </c>
       <c r="H10" t="s">
         <v>112</v>
       </c>
       <c r="I10" t="b">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -1109,14 +1110,14 @@
         <v>10</v>
       </c>
       <c r="G11" t="str">
-        <f>RIGHT(B11, 20)</f>
+        <f t="shared" si="0"/>
         <v>GCCTTCCCATCAGCACAGTT</v>
       </c>
       <c r="H11" t="s">
         <v>113</v>
       </c>
       <c r="I11" t="b">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -1137,14 +1138,14 @@
         <v>11</v>
       </c>
       <c r="G12" t="str">
-        <f>RIGHT(B12, 20)</f>
+        <f t="shared" si="0"/>
         <v>GGGTCAAGTCTTGATCGACA</v>
       </c>
       <c r="H12" t="s">
         <v>114</v>
       </c>
       <c r="I12" t="b">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -1165,14 +1166,14 @@
         <v>12</v>
       </c>
       <c r="G13" t="str">
-        <f>RIGHT(B13, 20)</f>
+        <f t="shared" si="0"/>
         <v>GAGCGGCATGCCCTCCTCGC</v>
       </c>
       <c r="H13" t="s">
         <v>116</v>
       </c>
       <c r="I13" t="b">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -1193,14 +1194,14 @@
         <v>13</v>
       </c>
       <c r="G14" t="str">
-        <f>RIGHT(B14, 20)</f>
+        <f t="shared" si="0"/>
         <v>GGCCTCCGTTCTTCAAGTCG</v>
       </c>
       <c r="H14" t="s">
         <v>117</v>
       </c>
       <c r="I14" t="b">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -1221,14 +1222,14 @@
         <v>14</v>
       </c>
       <c r="G15" t="str">
-        <f>RIGHT(B15, 20)</f>
+        <f t="shared" si="0"/>
         <v>GGGGAGGGCGCCTATGGGAA</v>
       </c>
       <c r="H15" t="s">
         <v>118</v>
       </c>
       <c r="I15" t="b">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -1439,323 +1440,323 @@
   <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.5" customWidth="1"/>
     <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="4" max="4" width="8.1640625" style="7" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="13.1640625" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="8.83203125" customWidth="1"/>
+    <col min="6" max="6" width="7.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="7" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A2">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="9">
         <v>54.302554000000001</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="9" t="s">
         <v>71</v>
       </c>
       <c r="G2" s="2"/>
     </row>
     <row r="3" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A3">
+      <c r="A3" s="6">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="9">
         <v>37.007700999999997</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="9" t="s">
         <v>71</v>
       </c>
       <c r="G3" s="2"/>
     </row>
     <row r="4" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A4">
+      <c r="A4" s="6">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="9">
         <v>34.814577999999997</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="9" t="s">
         <v>71</v>
       </c>
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A5">
+      <c r="A5" s="6">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="9">
         <v>39.735894000000002</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="9" t="s">
         <v>71</v>
       </c>
       <c r="G5" s="2"/>
     </row>
-    <row r="6" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A6">
+    <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="6">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="9">
         <v>25.903254</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="9" t="s">
         <v>71</v>
       </c>
       <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A7">
+      <c r="A7" s="6">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="9">
         <v>41.541404</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="9" t="s">
         <v>71</v>
       </c>
       <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" s="4" t="s">
+      <c r="A8" s="6">
+        <v>7</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="9">
         <v>71.254019</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="7" t="s">
         <v>88</v>
       </c>
       <c r="G8" s="2"/>
     </row>
     <row r="9" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" s="4" t="s">
+      <c r="A9" s="6">
+        <v>8</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="9">
         <v>69.879855000000006</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="7" t="s">
         <v>88</v>
       </c>
       <c r="G9" s="2"/>
     </row>
     <row r="10" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A10">
+      <c r="A10" s="6">
         <v>9</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="9">
         <v>33.375985</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="7" t="s">
         <v>88</v>
       </c>
       <c r="G10" s="2"/>
     </row>
-    <row r="11" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A11">
+    <row r="11" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="6">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="9">
         <v>39.518351000000003</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="7" t="s">
         <v>88</v>
       </c>
       <c r="G11" s="2"/>
     </row>
     <row r="12" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A12">
+      <c r="A12" s="6">
         <v>11</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="9">
         <v>23.940639999999998</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="9" t="s">
         <v>71</v>
       </c>
       <c r="G12" s="2"/>
     </row>
-    <row r="13" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A13">
+    <row r="13" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="6">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="9">
         <v>19.351908000000002</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="7" t="s">
         <v>88</v>
       </c>
       <c r="G13" s="2"/>
     </row>
     <row r="14" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A14">
+      <c r="A14" s="6">
         <v>13</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="9">
         <v>32.186906999999998</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="7" t="s">
         <v>88</v>
       </c>
       <c r="G14" s="2"/>
     </row>
     <row r="15" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A15">
+      <c r="A15" s="6">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="9">
         <v>50.834201999999998</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="7" t="s">
         <v>88</v>
       </c>
       <c r="G15" s="2"/>
